--- a/data/XRD/Mineral Categories.xlsx
+++ b/data/XRD/Mineral Categories.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="QkFQIdfGjVMqehYRuhVFDd8OIsHWyI0LWKU7GsV+X3k="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="uZfuiCY5BBOwB42DT8X5wc94pieBzltZZAdcJzkTIsQ="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="119">
   <si>
     <t>subtype</t>
   </si>
@@ -169,6 +169,12 @@
   </si>
   <si>
     <t>Qgypsum</t>
+  </si>
+  <si>
+    <t>XRD gypsum content (%)</t>
+  </si>
+  <si>
+    <t>Sulphates</t>
   </si>
   <si>
     <t>QHematite</t>
@@ -446,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -464,6 +470,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -720,6 +729,9 @@
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="C4" s="4" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -1031,12 +1043,16 @@
       <c r="A34" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
+      <c r="B34" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>49</v>
@@ -1045,7 +1061,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>49</v>
@@ -1054,29 +1070,29 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>39</v>
@@ -1084,10 +1100,10 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>39</v>
@@ -1095,10 +1111,10 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>39</v>
@@ -1106,10 +1122,10 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>7</v>
@@ -1117,10 +1133,10 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>7</v>
@@ -1128,10 +1144,10 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>7</v>
@@ -1139,10 +1155,10 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>7</v>
@@ -1150,10 +1166,10 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>7</v>
@@ -1161,7 +1177,7 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>49</v>
@@ -1170,19 +1186,19 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C49" s="4"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>23</v>
@@ -1190,10 +1206,10 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>23</v>
@@ -1201,10 +1217,10 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>23</v>
@@ -1212,10 +1228,10 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>23</v>
@@ -1223,14 +1239,14 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>6</v>
@@ -1241,10 +1257,10 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>39</v>
@@ -1252,17 +1268,17 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>7</v>
@@ -1270,10 +1286,10 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>7</v>
@@ -1281,10 +1297,10 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>7</v>
@@ -1292,10 +1308,10 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>7</v>
@@ -1303,10 +1319,10 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>7</v>
@@ -1314,10 +1330,10 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>23</v>
@@ -1325,10 +1341,10 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>23</v>
@@ -1336,10 +1352,10 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>23</v>
@@ -1347,10 +1363,10 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>23</v>
@@ -1358,10 +1374,10 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>23</v>
@@ -1369,7 +1385,7 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
@@ -1378,10 +1394,10 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>7</v>
@@ -1389,10 +1405,10 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>7</v>
@@ -1400,7 +1416,7 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>12</v>
@@ -1411,7 +1427,7 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>12</v>
@@ -1422,10 +1438,10 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>7</v>
@@ -1433,7 +1449,7 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>33</v>
@@ -1444,28 +1460,28 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C75" s="4"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C76" s="4"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>23</v>
@@ -1473,10 +1489,10 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>23</v>
@@ -1484,90 +1500,90 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C79" s="4"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C80" s="4"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="C81" s="4"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C83" s="4"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C84" s="4"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C85" s="4"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C86" s="4"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C87" s="4"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>39</v>

--- a/data/XRD/Mineral Categories.xlsx
+++ b/data/XRD/Mineral Categories.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="118">
   <si>
     <t>subtype</t>
   </si>
@@ -226,9 +226,6 @@
   </si>
   <si>
     <t>QMgCalcite</t>
-  </si>
-  <si>
-    <t>XRD magnesian calcite content (%)</t>
   </si>
   <si>
     <t>QMicroInt1</t>
@@ -1189,16 +1186,16 @@
         <v>69</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="C49" s="4"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>23</v>
@@ -1206,10 +1203,10 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>23</v>
@@ -1217,10 +1214,10 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>23</v>
@@ -1228,10 +1225,10 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>23</v>
@@ -1239,14 +1236,14 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>6</v>
@@ -1257,10 +1254,10 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>78</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>39</v>
@@ -1268,17 +1265,17 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>7</v>
@@ -1286,10 +1283,10 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>7</v>
@@ -1297,10 +1294,10 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>7</v>
@@ -1308,10 +1305,10 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>7</v>
@@ -1319,10 +1316,10 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>7</v>
@@ -1330,10 +1327,10 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>23</v>
@@ -1341,10 +1338,10 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>23</v>
@@ -1352,10 +1349,10 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>23</v>
@@ -1363,10 +1360,10 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>23</v>
@@ -1374,10 +1371,10 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>23</v>
@@ -1385,7 +1382,7 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
@@ -1394,10 +1391,10 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>7</v>
@@ -1405,10 +1402,10 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>7</v>
@@ -1416,7 +1413,7 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>12</v>
@@ -1427,7 +1424,7 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>12</v>
@@ -1438,7 +1435,7 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>63</v>
@@ -1449,7 +1446,7 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>33</v>
@@ -1460,28 +1457,28 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="C75" s="4"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="C76" s="4"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>23</v>
@@ -1489,10 +1486,10 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>23</v>
@@ -1500,90 +1497,90 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="C79" s="4"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C80" s="4"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C81" s="4"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C83" s="4"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C84" s="4"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C85" s="4"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C86" s="4"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C87" s="4"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>39</v>
